--- a/excel/boss.xlsx
+++ b/excel/boss.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
   <si>
     <t>编号</t>
   </si>
@@ -47,6 +47,15 @@
   </si>
   <si>
     <t>描述</t>
+  </si>
+  <si>
+    <t>血量</t>
+  </si>
+  <si>
+    <t>攻击力</t>
+  </si>
+  <si>
+    <t>移动速度</t>
   </si>
   <si>
     <t>id</t>
@@ -61,13 +70,22 @@
     <t>desc</t>
   </si>
   <si>
+    <t>hp</t>
+  </si>
+  <si>
+    <t>attack</t>
+  </si>
+  <si>
+    <t>speed</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
     <t>string</t>
   </si>
   <si>
-    <t>boss1</t>
+    <t>健身教练喵</t>
   </si>
   <si>
     <t>boss1描述xxxxxx</t>
@@ -1088,33 +1106,60 @@
       <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" ht="16.5" spans="1:13">
       <c r="A2" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:13">
       <c r="A3" s="4" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>9</v>
+        <v>15</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:13">
@@ -1122,17 +1167,23 @@
         <v>0</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3">
         <v>10</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="E4" s="3">
+        <v>500</v>
+      </c>
+      <c r="F4" s="3">
+        <v>12</v>
+      </c>
+      <c r="G4" s="3">
+        <v>350</v>
+      </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -1145,17 +1196,23 @@
         <v>1</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3">
         <v>11</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="E5" s="3">
+        <v>500</v>
+      </c>
+      <c r="F5" s="3">
+        <v>12</v>
+      </c>
+      <c r="G5" s="3">
+        <v>350</v>
+      </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -1168,17 +1225,23 @@
         <v>2</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C6" s="3">
         <v>12</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+        <v>21</v>
+      </c>
+      <c r="E6" s="3">
+        <v>500</v>
+      </c>
+      <c r="F6" s="3">
+        <v>13</v>
+      </c>
+      <c r="G6" s="3">
+        <v>350</v>
+      </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
@@ -1191,17 +1254,23 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C7" s="3">
         <v>13</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
+        <v>23</v>
+      </c>
+      <c r="E7" s="3">
+        <v>500</v>
+      </c>
+      <c r="F7" s="3">
+        <v>14</v>
+      </c>
+      <c r="G7" s="3">
+        <v>350</v>
+      </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>

--- a/excel/boss.xlsx
+++ b/excel/boss.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
   <si>
     <t>编号</t>
   </si>
@@ -58,6 +58,15 @@
     <t>移动速度</t>
   </si>
   <si>
+    <t>攻击距离</t>
+  </si>
+  <si>
+    <t>追击范围</t>
+  </si>
+  <si>
+    <t>有效范围</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -77,6 +86,15 @@
   </si>
   <si>
     <t>speed</t>
+  </si>
+  <si>
+    <t>attackDistance</t>
+  </si>
+  <si>
+    <t>chaseRange</t>
+  </si>
+  <si>
+    <t>validRange</t>
   </si>
   <si>
     <t>int</t>
@@ -1085,15 +1103,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M600"/>
+  <dimension ref="A1:N600"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="25.125" style="2" customWidth="1"/>
-    <col min="3" max="13" width="25.125" style="3" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="2"/>
+    <col min="3" max="14" width="25.125" style="3" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:13">
+    <row r="1" ht="16.5" spans="1:14">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1115,65 +1133,92 @@
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:13">
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:14">
       <c r="A2" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:13">
+        <v>16</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" spans="1:14">
       <c r="A3" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:13">
+        <v>20</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:14">
       <c r="A4" s="3">
         <v>0</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3">
         <v>10</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E4" s="3">
         <v>500</v>
@@ -1184,25 +1229,32 @@
       <c r="G4" s="3">
         <v>350</v>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
+      <c r="H4" s="3">
+        <v>200</v>
+      </c>
+      <c r="I4" s="3">
+        <v>350</v>
+      </c>
+      <c r="J4" s="3">
+        <v>1000</v>
+      </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:13">
+      <c r="N4" s="3"/>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:14">
       <c r="A5" s="3">
         <v>1</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C5" s="3">
         <v>11</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E5" s="3">
         <v>500</v>
@@ -1213,25 +1265,32 @@
       <c r="G5" s="3">
         <v>350</v>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
+      <c r="H5" s="3">
+        <v>200</v>
+      </c>
+      <c r="I5" s="3">
+        <v>350</v>
+      </c>
+      <c r="J5" s="3">
+        <v>1000</v>
+      </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:13">
+      <c r="N5" s="3"/>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:14">
       <c r="A6" s="3">
         <v>2</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C6" s="3">
         <v>12</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E6" s="3">
         <v>500</v>
@@ -1242,25 +1301,32 @@
       <c r="G6" s="3">
         <v>350</v>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
+      <c r="H6" s="3">
+        <v>200</v>
+      </c>
+      <c r="I6" s="3">
+        <v>350</v>
+      </c>
+      <c r="J6" s="3">
+        <v>1000</v>
+      </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:13">
+      <c r="N6" s="3"/>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:14">
       <c r="A7" s="3">
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C7" s="3">
         <v>13</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E7" s="3">
         <v>500</v>
@@ -1271,46 +1337,53 @@
       <c r="G7" s="3">
         <v>350</v>
       </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
+      <c r="H7" s="3">
+        <v>200</v>
+      </c>
+      <c r="I7" s="3">
+        <v>350</v>
+      </c>
+      <c r="J7" s="3">
+        <v>1000</v>
+      </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="N7" s="3"/>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:14">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:14">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:14">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:14">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:14">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:14">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:14">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:14">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
     </row>

--- a/excel/boss.xlsx
+++ b/excel/boss.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="32">
   <si>
     <t>编号</t>
   </si>
@@ -59,6 +59,9 @@
   </si>
   <si>
     <t>攻击距离</t>
+  </si>
+  <si>
+    <t>攻击间隔</t>
   </si>
   <si>
     <t>追击范围</t>
@@ -89,6 +92,9 @@
   </si>
   <si>
     <t>attackDistance</t>
+  </si>
+  <si>
+    <t>attackInterval</t>
   </si>
   <si>
     <t>chaseRange</t>
@@ -1103,15 +1109,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N600"/>
+  <dimension ref="A1:O600"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="25.125" style="2" customWidth="1"/>
-    <col min="3" max="14" width="25.125" style="3" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="2"/>
+    <col min="3" max="15" width="25.125" style="3" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:14">
+    <row r="1" ht="16.5" spans="1:15">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1142,83 +1148,92 @@
       <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:14">
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:15">
       <c r="A2" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:14">
+        <v>20</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" spans="1:15">
       <c r="A3" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:14">
+        <v>22</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:15">
       <c r="A4" s="3">
         <v>0</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C4" s="3">
         <v>10</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E4" s="3">
         <v>500</v>
@@ -1233,28 +1248,31 @@
         <v>200</v>
       </c>
       <c r="I4" s="3">
+        <v>2</v>
+      </c>
+      <c r="J4" s="3">
         <v>350</v>
       </c>
-      <c r="J4" s="3">
+      <c r="K4" s="3">
         <v>1000</v>
       </c>
-      <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:14">
+      <c r="O4" s="3"/>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:15">
       <c r="A5" s="3">
         <v>1</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3">
         <v>11</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E5" s="3">
         <v>500</v>
@@ -1269,28 +1287,31 @@
         <v>200</v>
       </c>
       <c r="I5" s="3">
+        <v>2</v>
+      </c>
+      <c r="J5" s="3">
         <v>350</v>
       </c>
-      <c r="J5" s="3">
+      <c r="K5" s="3">
         <v>1000</v>
       </c>
-      <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:14">
+      <c r="O5" s="3"/>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:15">
       <c r="A6" s="3">
         <v>2</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C6" s="3">
         <v>12</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E6" s="3">
         <v>500</v>
@@ -1305,28 +1326,31 @@
         <v>200</v>
       </c>
       <c r="I6" s="3">
+        <v>2</v>
+      </c>
+      <c r="J6" s="3">
         <v>350</v>
       </c>
-      <c r="J6" s="3">
+      <c r="K6" s="3">
         <v>1000</v>
       </c>
-      <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:14">
+      <c r="O6" s="3"/>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:15">
       <c r="A7" s="3">
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C7" s="3">
         <v>13</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E7" s="3">
         <v>500</v>
@@ -1341,49 +1365,52 @@
         <v>200</v>
       </c>
       <c r="I7" s="3">
+        <v>2</v>
+      </c>
+      <c r="J7" s="3">
         <v>350</v>
       </c>
-      <c r="J7" s="3">
+      <c r="K7" s="3">
         <v>1000</v>
       </c>
-      <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7" s="3"/>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:15">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:15">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:15">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:15">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:15">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:15">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:15">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:15">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
     </row>

--- a/excel/boss.xlsx
+++ b/excel/boss.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="34">
   <si>
     <t>编号</t>
   </si>
@@ -70,6 +70,9 @@
     <t>有效范围</t>
   </si>
   <si>
+    <t>怒气值</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -101,6 +104,9 @@
   </si>
   <si>
     <t>validRange</t>
+  </si>
+  <si>
+    <t>rage</t>
   </si>
   <si>
     <t>int</t>
@@ -1151,75 +1157,84 @@
       <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2" ht="16.5" spans="1:15">
       <c r="A2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:15">
       <c r="A3" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:15">
@@ -1227,13 +1242,13 @@
         <v>0</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3">
         <v>10</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E4" s="3">
         <v>500</v>
@@ -1256,7 +1271,9 @@
       <c r="K4" s="3">
         <v>1000</v>
       </c>
-      <c r="L4" s="3"/>
+      <c r="L4" s="3">
+        <v>100</v>
+      </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
@@ -1266,13 +1283,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C5" s="3">
         <v>11</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E5" s="3">
         <v>500</v>
@@ -1295,7 +1312,9 @@
       <c r="K5" s="3">
         <v>1000</v>
       </c>
-      <c r="L5" s="3"/>
+      <c r="L5" s="3">
+        <v>40</v>
+      </c>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
@@ -1305,13 +1324,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C6" s="3">
         <v>12</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E6" s="3">
         <v>500</v>
@@ -1334,7 +1353,9 @@
       <c r="K6" s="3">
         <v>1000</v>
       </c>
-      <c r="L6" s="3"/>
+      <c r="L6" s="3">
+        <v>120</v>
+      </c>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
@@ -1344,13 +1365,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C7" s="3">
         <v>13</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E7" s="3">
         <v>500</v>
@@ -1373,7 +1394,9 @@
       <c r="K7" s="3">
         <v>1000</v>
       </c>
-      <c r="L7" s="3"/>
+      <c r="L7" s="3">
+        <v>80</v>
+      </c>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>

--- a/excel/boss.xlsx
+++ b/excel/boss.xlsx
@@ -1260,7 +1260,7 @@
         <v>350</v>
       </c>
       <c r="H4" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I4" s="3">
         <v>2</v>
@@ -1301,7 +1301,7 @@
         <v>350</v>
       </c>
       <c r="H5" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="I5" s="3">
         <v>2</v>
@@ -1342,7 +1342,7 @@
         <v>350</v>
       </c>
       <c r="H6" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="I6" s="3">
         <v>2</v>
@@ -1383,7 +1383,7 @@
         <v>350</v>
       </c>
       <c r="H7" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="I7" s="3">
         <v>2</v>
